--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.0572736252368</v>
+        <v>3.909306964100979</v>
       </c>
       <c r="D2" t="n">
-        <v>25.3293000751325</v>
+        <v>4.116011262209032</v>
       </c>
       <c r="E2" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F2" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.24914749041809</v>
+        <v>5.40298646719294</v>
       </c>
       <c r="D3" t="n">
-        <v>31.91099178422819</v>
+        <v>5.185536164937082</v>
       </c>
       <c r="E3" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F3" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.76453412926082</v>
+        <v>3.699236796004883</v>
       </c>
       <c r="D4" t="n">
-        <v>21.59620959121805</v>
+        <v>3.509384058572933</v>
       </c>
       <c r="E4" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F4" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.48738997426344</v>
+        <v>4.629200870817809</v>
       </c>
       <c r="D5" t="n">
-        <v>28.54656630307452</v>
+        <v>4.638817024249611</v>
       </c>
       <c r="E5" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F5" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.19348007178824</v>
+        <v>6.693940511665589</v>
       </c>
       <c r="D6" t="n">
-        <v>40.5103675807915</v>
+        <v>6.58293473187862</v>
       </c>
       <c r="E6" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F6" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.768505506990914</v>
+        <v>1.587382144886024</v>
       </c>
       <c r="D7" t="n">
-        <v>8.441289636448147</v>
+        <v>1.371709565922824</v>
       </c>
       <c r="E7" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F7" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.15159292497471</v>
+        <v>2.78713385030839</v>
       </c>
       <c r="D8" t="n">
-        <v>14.53444185374863</v>
+        <v>2.361846801234153</v>
       </c>
       <c r="E8" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F8" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.90251378996816</v>
+        <v>2.909158490869826</v>
       </c>
       <c r="D9" t="n">
-        <v>33.42664261107183</v>
+        <v>5.431829424299172</v>
       </c>
       <c r="E9" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F9" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.124143795447329</v>
+        <v>1.482673366760191</v>
       </c>
       <c r="D10" t="n">
-        <v>25.34758371127315</v>
+        <v>4.118982353081887</v>
       </c>
       <c r="E10" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F10" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.40121946685673</v>
+        <v>2.665198163364218</v>
       </c>
       <c r="D11" t="n">
-        <v>13.82931668593933</v>
+        <v>2.247263961465142</v>
       </c>
       <c r="E11" t="n">
-        <v>9.637816323149147</v>
+        <v>1.566145152511736</v>
       </c>
       <c r="F11" t="n">
-        <v>9.423254217729649</v>
+        <v>1.531278810381068</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
